--- a/cs-492-BMS/Robby's Requirements.xlsx
+++ b/cs-492-BMS/Robby's Requirements.xlsx
@@ -8,12 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\these\OneDrive\Desktop\School\CS492 Team Project 2\CS-492-Team-Project\cs-492-BMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E21F098-64C6-4631-9391-BB8C3A85D78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A604CE-D81B-457D-857A-76DC0866AD62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="270" windowWidth="29010" windowHeight="13755" xr2:uid="{29DFB9AA-CDFA-421F-AD48-D547230F00D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{29DFB9AA-CDFA-421F-AD48-D547230F00D9}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="2. Inventory Browser" sheetId="1" r:id="rId1"/>
+    <sheet name="3. Inventory Update System" sheetId="2" r:id="rId2"/>
+    <sheet name="4. Cart System" sheetId="3" r:id="rId3"/>
+    <sheet name="5. Order Processing (Customer)" sheetId="4" r:id="rId4"/>
+    <sheet name="6. Order Processing (Manufactur" sheetId="5" r:id="rId5"/>
+    <sheet name="10. Inventory Search Feature" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,6 +41,119 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="36">
+  <si>
+    <t>Given a customer, when they open the inventory page, then a list of available books is displayed</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Criteria</t>
+  </si>
+  <si>
+    <t>Shows out of stock books too, will fix</t>
+  </si>
+  <si>
+    <t>Given inventory exists, then each item shows title, price, and availability</t>
+  </si>
+  <si>
+    <t>Shows negative numbers, requires test cases</t>
+  </si>
+  <si>
+    <t>Given no inventory, then a "no items available" message is shwon</t>
+  </si>
+  <si>
+    <t>Given an admin, when they update ivnentory manually, then the system reflect the new quantity</t>
+  </si>
+  <si>
+    <t>No notes</t>
+  </si>
+  <si>
+    <t>Given a purchase occurs, when checkout completes, then inventory is reduced automatically</t>
+  </si>
+  <si>
+    <t>Given inventory reaches zero, then the item is marked as out of stock</t>
+  </si>
+  <si>
+    <t>displays negative numbers, but it is technically out of stock</t>
+  </si>
+  <si>
+    <t>Given invalid input (e.g. negative stock), then the system rejects the update</t>
+  </si>
+  <si>
+    <t>Untested</t>
+  </si>
+  <si>
+    <t>• Given a customer, when they add an item, then it appears in the cart</t>
+  </si>
+  <si>
+    <t>• Given items in cart, when the user leaves and returns, then the cart persists (session or account-based)</t>
+  </si>
+  <si>
+    <t>• Given a cart item, when removed, then it no longer appears in the cart</t>
+  </si>
+  <si>
+    <t>• Given duplicate items added, then quantity updates instead of duplicating entries</t>
+  </si>
+  <si>
+    <t>This is session based not account based and I will not do account based</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>• Given items in cart, when checkout is completed, then an order is created</t>
+  </si>
+  <si>
+    <t>• Given valid payment, then the transaction is processed successfully</t>
+  </si>
+  <si>
+    <t>• Given failed payment, then the order is not completed and user is notified</t>
+  </si>
+  <si>
+    <t>• Given a completed order, then confirmation is displayed and/or emailed</t>
+  </si>
+  <si>
+    <t>It's called a sale in our implementation</t>
+  </si>
+  <si>
+    <t>All payment is currently valid</t>
+  </si>
+  <si>
+    <t>Need to figure out how to fake an invalid payment</t>
+  </si>
+  <si>
+    <t>No Notes</t>
+  </si>
+  <si>
+    <t>No emails</t>
+  </si>
+  <si>
+    <t>• Given an admin, when they place a restock order, then a purchase order is created</t>
+  </si>
+  <si>
+    <t>• Given a restock order, when fulfilled, then inventory increases accordingly</t>
+  </si>
+  <si>
+    <t>• Given invalid order data, then the system prevents submission</t>
+  </si>
+  <si>
+    <t>• Given a search query, when entered, then matching inventory items are displayed</t>
+  </si>
+  <si>
+    <t>• Given no matches, then a “no results found” message appears</t>
+  </si>
+  <si>
+    <t>• Given partial matches, then relevant results are returned</t>
+  </si>
+  <si>
+    <t>• Given search results, then users can select items to view details</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69,8 +187,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -86,6 +224,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -405,9 +560,1606 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54987C7F-0E1F-4D70-81E1-0100C7E8A815}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="37.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="5"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="5"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="5"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="5"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="5"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="5"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="5"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="5"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67572BCF-FC7F-4807-A2AC-6D9ED7E1980A}">
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="5"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="5"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="5"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="5"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="5"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="5"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="5"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="5"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{989202B8-DE7C-42D4-AA58-295D402B3D4B}">
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="5"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="5"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="5"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="5"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="5"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="5"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="5"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="5"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F00A870-C4D3-4147-AE03-D6E4F7F5DCAD}">
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="5"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="5"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="5"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="5"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="5"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="5"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="5"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="5"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F278BE2-4EF3-4F57-A500-AB11FF1DCC9E}">
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="5"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="5"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="5"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="5"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="5"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="5"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="5"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="5"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA727F0-6E72-473B-B163-2E427B9AE1C0}">
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="37.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4"/>
+      <c r="B7" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="5"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="5"/>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="5"/>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="5"/>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="5"/>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5"/>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5"/>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="5"/>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="5"/>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="5"/>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="5"/>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="5"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/cs-492-BMS/Robby's Requirements.xlsx
+++ b/cs-492-BMS/Robby's Requirements.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\these\OneDrive\Desktop\School\CS492 Team Project 2\CS-492-Team-Project\cs-492-BMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A604CE-D81B-457D-857A-76DC0866AD62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28281F9-56C6-4BBD-ADAC-E7AB953FD78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{29DFB9AA-CDFA-421F-AD48-D547230F00D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{29DFB9AA-CDFA-421F-AD48-D547230F00D9}"/>
   </bookViews>
   <sheets>
     <sheet name="2. Inventory Browser" sheetId="1" r:id="rId1"/>
@@ -1408,7 +1408,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>26</v>
